--- a/Result/profitability/2545.xlsx
+++ b/Result/profitability/2545.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04875</v>
+        <v>0.8925</v>
       </c>
       <c r="N2" t="n">
-        <v>36.56375</v>
+        <v>36.47625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6725</v>
+        <v>0.74375</v>
       </c>
       <c r="N3" t="n">
-        <v>35.79625</v>
+        <v>34.7825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.7775000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>33.48</v>
+        <v>32.5675</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6625000000000001</v>
+        <v>0.5462499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>30.9125</v>
+        <v>30.73625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.36875</v>
+        <v>0.69125</v>
       </c>
       <c r="N6" t="n">
-        <v>28.7975</v>
+        <v>30.825</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7524999999999999</v>
+        <v>1.0825</v>
       </c>
       <c r="N7" t="n">
-        <v>30.06875</v>
+        <v>32.51</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9512499999999999</v>
+        <v>1.20875</v>
       </c>
       <c r="N8" t="n">
-        <v>30.7375</v>
+        <v>33.7125</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1518,7 +1518,7 @@
         <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0.98375</v>
+        <v>0.9837499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>31.68125</v>
@@ -1645,7 +1645,7 @@
         <v>-0.02</v>
       </c>
       <c r="M10" t="n">
-        <v>0.805</v>
+        <v>0.8049999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>28.0875</v>
@@ -1899,7 +1899,7 @@
         <v>0.11</v>
       </c>
       <c r="M12" t="n">
-        <v>0.74125</v>
+        <v>0.7412500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>27.44375</v>
@@ -2026,7 +2026,7 @@
         <v>0.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0.63125</v>
+        <v>0.6312500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>27.56</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2545</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1596</v>
+      </c>
+      <c r="D75" t="n">
+        <v>947</v>
+      </c>
+      <c r="E75" t="n">
+        <v>649</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>339</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>518</v>
+      </c>
+      <c r="J75" t="n">
+        <v>857</v>
+      </c>
+      <c r="K75" t="n">
+        <v>777</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.12875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.40625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-206</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.411625148279952</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.9300000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3120805369127517</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.410000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0335155692892799</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
